--- a/output/第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx
+++ b/output/第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>第115条の48第1項の会議は地域ケア会議である。当方は地域ケア会議の代表指標及び記録様式を整理しているが（確認事項No.118からNo.122まで）、他の法律に基づく会議との連携、地域包括支援センターへの委託、地域の住民の意見の反映はいずれも把握していなかった。</t>
+          <t>第115条の48第1項の会議は地域ケア会議である。当方は地域ケア会議の代表指標及び記録様式を整理しているが（確認事項No.118からNo.122まで）、他の法律に基づく会議との連携、地域包括支援センターへの委託、地域の住民の意見の反映はいずれも把握していなかった。【令和8年10月15日】新旧対照条文により、改正後は見出し及び第1項の定義が「支援会議」に改められ、構成員として地域包括支援センターが明示されることを確かめた（現行は「関係機関及び関係団体」）。連携の対象となる会議の根拠は、社会福祉法第106条の3の2第1項、障害者総合支援法第89条の3第1項、住宅確保要配慮者に対する賃貸住宅の供給の促進に関する法律第81条第1項及び生活困窮者自立支援法第9条第1項である。</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>（1）次の事項を定めるものとする（第117条第2項第3号・第4号）。イ 介護給付等対象サービスの種類ごとの量及び地域支援事業の量に関する中長期的な推計　ロ 介護給付等対象サービスを提供する体制の確保及び地域支援事業の実施に関し、中長期的な観点から市町村が取り組むべき施策に関する事項。（2）次の事項を定めるよう努めるものとする（第117条第3項第4号・第5号）。イ 生産性の向上、介護支援専門員その他の従事者の確保及び資質の向上その他の質の高いサービスの提供の確保と安定した経営基盤の確立の双方の実現を図る取組に資する都道府県と連携した取組　ロ 介護支援専門員その他の地域支援事業に従事する者の確保及び資質の向上に資する都道府県と連携した取組　ハ 地域支援事業の実施における生産性の向上に資する都道府県と連携した取組。（3）第2項第1号及び第2号並びに（1）イを定めるに当たっては、イ 当該市町村が定める区域ごとの有料老人ホーム（老人福祉法第29条第1項の届出が行われているもの）及び登録有料老人ホーム並びに高齢者の居住の安定確保に関する法律に規定する登録住宅のそれぞれの入居定員総数　ロ 当該市町村が属する都道府県が定める区域ごとの医療に関する専門的知識を有する者と介護サービス事業者、居宅における医療を提供する医療機関その他の関係者との連携の状況　を勘案しなければならない（第117条第5項）。（4）（1）イを定め、又は変更しようとするときは、あらかじめ、都道府県の意見を聴かなければならない（第117条第14項）。</t>
+          <t>（1）次の事項を定めるものとする（第117条第2項第3号・第4号）。イ 介護給付等対象サービスの種類ごとの量及び地域支援事業の量に関する中長期的な推計　ロ 介護給付等対象サービスを提供する体制の確保及び地域支援事業の実施に関し、中長期的な観点から市町村が取り組むべき施策に関する事項。（2）次の事項を定めるよう努めるものとする（第117条第3項第4号・第4号の2・第5号）。イ 生産性の向上、介護支援専門員その他の従事者の確保及び資質の向上その他の質の高いサービスの提供の確保と安定した経営基盤の確立の双方の実現を図る取組に資する都道府県と連携した取組　ロ 介護支援専門員その他の地域支援事業に従事する者の確保及び資質の向上に資する都道府県と連携した取組　ハ 地域支援事業の実施における生産性の向上に資する都道府県と連携した取組。（3）第2項第1号から第3号までに掲げる事項（第1号及び第2号並びに（1）イ）を定めるに当たっては、イ 当該市町村が定める区域ごとの有料老人ホーム（老人福祉法第29条第1項の届出が行われているもの）及び登録有料老人ホーム並びに高齢者の居住の安定確保に関する法律に規定する登録住宅のそれぞれの入居定員総数　ロ 当該市町村が属する都道府県が定める区域ごとの医療に関する専門的知識を有する者と介護サービス事業者、居宅における医療を提供する医療機関その他の関係者との連携の状況　を勘案しなければならない（第117条第5項）。（4）第2項第1号から第3号までに掲げる事項に係る部分を定め、又は変更しようとするときは、あらかじめ、都道府県の意見を聴かなければならない（第117条第14項）。（5）従前は定めるよう努めるものとされていた中長期的な推計のうち、サービスの種類ごとの量及び地域支援事業の量が（1）イへ移り、第3項第3号には保険給付に要する費用の額、地域支援事業に要する費用の額及び保険料の水準が残る。</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>号及び項が確定した（従前は［要確認］としていた）。当方は中長期的な推計の反映先を「第2章第8節」としていたが、サービスの種類ごとの量及び給付費は第6章第2節・第3節にある。地域支援事業の量の中長期的な推計は算定していなかった。第3項第4号・第5号は「都道府県と連携した取組」であり3項目ある。第5項の勘案は「区域ごと」の入居定員総数である。第14項（都道府県の意見）は把握していなかった。</t>
+          <t>号及び項が確定した（従前は［要確認］としていた）。当方は中長期的な推計の反映先を「第2章第8節」としていたが、サービスの種類ごとの量及び給付費は第6章第2節・第3節にある。地域支援事業の量の中長期的な推計は算定していなかった。第3項第4号・第5号は「都道府県と連携した取組」であり3項目ある。第5項の勘案は「区域ごと」の入居定員総数である。第14項（都道府県の意見）は把握していなかった。【令和8年10月15日】新旧対照条文により次を確かめた。①（2）の号は第4号・第4号の2・第5号である②（3）（4）の対象はいずれも第2項第1号から第3号までであり、（4）は現行でも第1号及び第2号が対象である（改正により第3号が加わる）③第3項第3号は改正前からあり、量が（1）イへ移ったうえで費用の額及び保険料の水準が残る（量は義務、費用の額及び保険料の水準は努力義務である）④有料老人ホーム及び登録住宅の入居定員総数は第3項第9号（記載事項）にも定められており、記載事項と勘案事項の二重の構造である⑤「登録有料老人ホーム」が第3項第9号及び第5項第1号に加わるのは第4条関係（2年以内）であり、第10期計画の策定の時点では加わらない。</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>当方は「介護分野における生産性向上推進のための協議会」としていたが、原典の名称は協議会であり、その目的は質の高い介護サービスの提供の確保と安定した経営基盤の確立の双方の実現を図る取組の促進である。構成員に市町村が明記されているため、「参画し、又はその支援を受ける立場」ではなく構成員として参画する。社会福祉法第92条の2の社会福祉事業等従事者の確保のための協議会（置くよう努める）とは別の協議会である。</t>
+          <t>当方は「介護分野における生産性向上推進のための協議会」としていたが、原典の名称は協議会であり、その目的は質の高い介護サービスの提供の確保と安定した経営基盤の確立の双方の実現を図る取組の促進である。構成員に市町村が明記されているため、「参画し、又はその支援を受ける立場」ではなく構成員として参画する。社会福祉法第92条の2の社会福祉事業等従事者の確保のための協議会（置くよう努める）とは別の協議会である。【令和8年10月15日】新旧対照条文により次を確かめた。①都道府県センターの根拠は社会福祉法第93条第1項である②当該都道府県に社会福祉法第92条の2に規定する協議会が置かれている場合には、当該協議会における協議の結果を尊重しなければならない（第120条の4第2項）③都道府県及び協議会を構成する関係機関は、協議の結果に基づき、当該協議をした方策に係る取組を連携して行うものとする（同条第3項）④組織及び運営に関し必要な事項は第120条の5による。</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>当方は「登録施設介護支援等に係る利用者負担の在り方は引き続き検討することとされています」としていたが、費用の額は100分の90と法律で定められている。検討されているのは一定以上の所得を有する者に係る負担割合であり、法律で定まっている部分と検討中の部分を分けて記載する。登録施設介護予防支援を地域包括支援センターの職員が行うことは包括的支援事業の業務量に関わる。</t>
+          <t>当方は「登録施設介護支援等に係る利用者負担の在り方は引き続き検討することとされています」としていたが、費用の額は100分の90と法律で定められている。検討されているのは一定以上の所得を有する者に係る負担割合であり、法律で定まっている部分と検討中の部分を分けて記載する。登録施設介護予防支援を地域包括支援センターの職員が行うことは包括的支援事業の業務量に関わる。【令和8年10月15日】新旧対照条文により、市町村介護保険事業計画の任意記載事項である事業者相互間の連携の確保に関する事業に指定登録施設介護支援及び指定登録施設介護予防支援の事業が加わり（第117条第3項第6号・第7号）、市町村が行うことができる保健福祉事業に指定登録施設介護支援の事業が加わること（第115条の49）を確かめた。いずれも把握していなかった。</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の条文。要綱により号及び項は判明したが、条文の文言を確認できていない（確認事項No.181）。</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>介護保険法第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の条文。要綱により号及び項は判明したが、条文の文言を確認できていない（確認事項No.181）。【令和8年10月15日　一部受領】新旧対照条文により改正後の条文を確認した。参照条文（全45頁）も受領したが、条文の部分は画像であり内容を確認できていない。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>改正前後の対照。要綱は改正事項の要旨であり、改正後の条文の全体を確認できない。</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>改正前後の対照。要綱は改正事項の要旨であり、改正後の条文の全体を確認できない。【令和8年10月15日　受領】新旧対照条文（全353頁）により改正後の条文を確認した（優先度は解消）。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
     </row>
